--- a/GRClass_API_Tracker.xlsx
+++ b/GRClass_API_Tracker.xlsx
@@ -12,12 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1633" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1619" uniqueCount="519">
   <si>
     <t>🚢  GR-Class Maritime Certification System — Complete API Progress Tracker</t>
   </si>
   <si>
-    <t>Last Updated: 15 Apr 2026  |  Total APIs: 220  |  Modules: 35</t>
+    <t>Last Updated: 21 May 2026  |  Total APIs: 218  |  Modules: 35</t>
   </si>
   <si>
     <t>#</t>
@@ -416,15 +416,6 @@
     <t>ADMIN,TO</t>
   </si>
   <si>
-    <t>/api/v1/jobs/:id/send-back</t>
-  </si>
-  <si>
-    <t>Send job back for corrections</t>
-  </si>
-  <si>
-    <t>ADMIN,TM,TO</t>
-  </si>
-  <si>
     <t>/api/v1/jobs/:id/reject</t>
   </si>
   <si>
@@ -629,271 +620,265 @@
     <t>List all certificates (with filters)</t>
   </si>
   <si>
-    <t>/api/v1/certificates/expiring</t>
-  </si>
-  <si>
-    <t>List expiring certificates</t>
+    <t>/api/v1/certificates/upload-url</t>
+  </si>
+  <si>
+    <t>Get presigned URL to upload certificate file</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/vessel/:vesselId/external</t>
+  </si>
+  <si>
+    <t>Upload externally issued certificate</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/vessel/:vesselId</t>
+  </si>
+  <si>
+    <t>Get all certificates for a vessel</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/job/:jobId</t>
+  </si>
+  <si>
+    <t>Get certificate generated from a job</t>
+  </si>
+  <si>
+    <t>Generate certificate draft from job</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/:id</t>
+  </si>
+  <si>
+    <t>Update certificate draft fields</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/:id/issue</t>
+  </si>
+  <si>
+    <t>Officially issue certificate</t>
+  </si>
+  <si>
+    <t>Get certificate full details</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/:id/preview</t>
+  </si>
+  <si>
+    <t>Preview certificate as PDF</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/:id/download</t>
+  </si>
+  <si>
+    <t>Download certificate PDF</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/:id/sign</t>
+  </si>
+  <si>
+    <t>Digitally sign the certificate</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/:id/signature</t>
+  </si>
+  <si>
+    <t>Get signature info for certificate</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/:id/suspend</t>
+  </si>
+  <si>
+    <t>Suspend an active certificate</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/:id/revoke</t>
+  </si>
+  <si>
+    <t>Revoke certificate permanently</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/:id/restore</t>
+  </si>
+  <si>
+    <t>Restore suspended certificate</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/:id/renew</t>
+  </si>
+  <si>
+    <t>Renew expiring certificate</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/bulk-renew</t>
+  </si>
+  <si>
+    <t>Bulk renew multiple certificates</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/:id/reissue</t>
+  </si>
+  <si>
+    <t>Reissue certificate (new version)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  🏛️ Certificate Authorities   [/api/v1/certificates/authorities]</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/authorities</t>
+  </si>
+  <si>
+    <t>List certificate authorities</t>
+  </si>
+  <si>
+    <t>Add new certificate authority</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/authorities/upload-logo</t>
+  </si>
+  <si>
+    <t>Get presigned URL for CA logo</t>
+  </si>
+  <si>
+    <t>/api/v1/certificates/authorities/:id</t>
+  </si>
+  <si>
+    <t>Get certificate authority details</t>
+  </si>
+  <si>
+    <t>Update certificate authority</t>
+  </si>
+  <si>
+    <t>Delete certificate authority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  📄 Documents   [/api/v1/documents]</t>
+  </si>
+  <si>
+    <t>/api/v1/documents/get-upload-url</t>
+  </si>
+  <si>
+    <t>Get S3 presigned URL for file upload</t>
+  </si>
+  <si>
+    <t>CLIENT,ADMIN,GM,TM,SURV</t>
+  </si>
+  <si>
+    <t>/api/v1/documents/upload</t>
+  </si>
+  <si>
+    <t>Upload file directly (multipart)</t>
+  </si>
+  <si>
+    <t>/api/v1/documents/register</t>
+  </si>
+  <si>
+    <t>Register file after S3 direct upload</t>
+  </si>
+  <si>
+    <t>/api/v1/documents/:id</t>
+  </si>
+  <si>
+    <t>Get document metadata by ID</t>
+  </si>
+  <si>
+    <t>/api/v1/documents/:entityType/:entityId</t>
+  </si>
+  <si>
+    <t>List all docs for an entity (job/vessel)</t>
+  </si>
+  <si>
+    <t>Upload document for specific entity</t>
+  </si>
+  <si>
+    <t>/api/v1/documents/:entityType/:entityId/register</t>
+  </si>
+  <si>
+    <t>Register doc for entity post-S3 upload</t>
+  </si>
+  <si>
+    <t>Delete a document</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  🔔 Notifications   [/api/v1/notifications]</t>
+  </si>
+  <si>
+    <t>/api/v1/notifications</t>
+  </si>
+  <si>
+    <t>Get own notifications list</t>
+  </si>
+  <si>
+    <t>/api/v1/notifications/:id/read</t>
+  </si>
+  <si>
+    <t>Mark single notification as read</t>
+  </si>
+  <si>
+    <t>/api/v1/notifications/read-all</t>
+  </si>
+  <si>
+    <t>Mark all notifications as read</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ✔️ Approvals   [/api/v1/approvals]</t>
+  </si>
+  <si>
+    <t>/api/v1/approvals</t>
+  </si>
+  <si>
+    <t>Create multi-step approval workflow</t>
+  </si>
+  <si>
+    <t>/api/v1/approvals/:id/step</t>
+  </si>
+  <si>
+    <t>Approve / reject a specific step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  ⚠️ Non-Conformities   [/api/v1/non-conformities]</t>
+  </si>
+  <si>
+    <t>/api/v1/non-conformities</t>
+  </si>
+  <si>
+    <t>Report a non-conformity finding</t>
+  </si>
+  <si>
+    <t>SURVEYOR,TO</t>
+  </si>
+  <si>
+    <t>/api/v1/non-conformities/:id/close</t>
+  </si>
+  <si>
+    <t>Close / resolve NC after correction</t>
+  </si>
+  <si>
+    <t>TO,TM</t>
+  </si>
+  <si>
+    <t>/api/v1/non-conformities/job/:jobId</t>
+  </si>
+  <si>
+    <t>Get all NCs for a job</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  🚨 Incidents   [/api/v1/incidents]</t>
+  </si>
+  <si>
+    <t>/api/v1/incidents</t>
+  </si>
+  <si>
+    <t>Report a new incident</t>
+  </si>
+  <si>
+    <t>CLIENT,ADMIN,GM,TM</t>
+  </si>
+  <si>
+    <t>List all incidents</t>
   </si>
   <si>
     <t>CLIENT,ADMIN,GM,TM,TO</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/upload-url</t>
-  </si>
-  <si>
-    <t>Get presigned URL to upload certificate file</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/vessel/:vesselId/external</t>
-  </si>
-  <si>
-    <t>Upload externally issued certificate</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/vessel/:vesselId</t>
-  </si>
-  <si>
-    <t>Get all certificates for a vessel</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/job/:jobId</t>
-  </si>
-  <si>
-    <t>Get certificate generated from a job</t>
-  </si>
-  <si>
-    <t>Generate certificate draft from job</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/:id</t>
-  </si>
-  <si>
-    <t>Update certificate draft fields</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/:id/issue</t>
-  </si>
-  <si>
-    <t>Officially issue certificate</t>
-  </si>
-  <si>
-    <t>Get certificate full details</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/:id/preview</t>
-  </si>
-  <si>
-    <t>Preview certificate as PDF</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/:id/download</t>
-  </si>
-  <si>
-    <t>Download certificate PDF</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/:id/sign</t>
-  </si>
-  <si>
-    <t>Digitally sign the certificate</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/:id/signature</t>
-  </si>
-  <si>
-    <t>Get signature info for certificate</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/:id/suspend</t>
-  </si>
-  <si>
-    <t>Suspend an active certificate</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/:id/revoke</t>
-  </si>
-  <si>
-    <t>Revoke certificate permanently</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/:id/restore</t>
-  </si>
-  <si>
-    <t>Restore suspended certificate</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/:id/renew</t>
-  </si>
-  <si>
-    <t>Renew expiring certificate</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/bulk-renew</t>
-  </si>
-  <si>
-    <t>Bulk renew multiple certificates</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/:id/reissue</t>
-  </si>
-  <si>
-    <t>Reissue certificate (new version)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  🏛️ Certificate Authorities   [/api/v1/certificates/authorities]</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/authorities</t>
-  </si>
-  <si>
-    <t>List certificate authorities</t>
-  </si>
-  <si>
-    <t>Add new certificate authority</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/authorities/upload-logo</t>
-  </si>
-  <si>
-    <t>Get presigned URL for CA logo</t>
-  </si>
-  <si>
-    <t>/api/v1/certificates/authorities/:id</t>
-  </si>
-  <si>
-    <t>Get certificate authority details</t>
-  </si>
-  <si>
-    <t>Update certificate authority</t>
-  </si>
-  <si>
-    <t>Delete certificate authority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  📄 Documents   [/api/v1/documents]</t>
-  </si>
-  <si>
-    <t>/api/v1/documents/get-upload-url</t>
-  </si>
-  <si>
-    <t>Get S3 presigned URL for file upload</t>
-  </si>
-  <si>
-    <t>CLIENT,ADMIN,GM,TM,SURV</t>
-  </si>
-  <si>
-    <t>/api/v1/documents/upload</t>
-  </si>
-  <si>
-    <t>Upload file directly (multipart)</t>
-  </si>
-  <si>
-    <t>/api/v1/documents/register</t>
-  </si>
-  <si>
-    <t>Register file after S3 direct upload</t>
-  </si>
-  <si>
-    <t>/api/v1/documents/:id</t>
-  </si>
-  <si>
-    <t>Get document metadata by ID</t>
-  </si>
-  <si>
-    <t>/api/v1/documents/:entityType/:entityId</t>
-  </si>
-  <si>
-    <t>List all docs for an entity (job/vessel)</t>
-  </si>
-  <si>
-    <t>Upload document for specific entity</t>
-  </si>
-  <si>
-    <t>/api/v1/documents/:entityType/:entityId/register</t>
-  </si>
-  <si>
-    <t>Register doc for entity post-S3 upload</t>
-  </si>
-  <si>
-    <t>Delete a document</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  🔔 Notifications   [/api/v1/notifications]</t>
-  </si>
-  <si>
-    <t>/api/v1/notifications</t>
-  </si>
-  <si>
-    <t>Get own notifications list</t>
-  </si>
-  <si>
-    <t>/api/v1/notifications/:id/read</t>
-  </si>
-  <si>
-    <t>Mark single notification as read</t>
-  </si>
-  <si>
-    <t>/api/v1/notifications/read-all</t>
-  </si>
-  <si>
-    <t>Mark all notifications as read</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ✔️ Approvals   [/api/v1/approvals]</t>
-  </si>
-  <si>
-    <t>/api/v1/approvals</t>
-  </si>
-  <si>
-    <t>Create multi-step approval workflow</t>
-  </si>
-  <si>
-    <t>/api/v1/approvals/:id/step</t>
-  </si>
-  <si>
-    <t>Approve / reject a specific step</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  ⚠️ Non-Conformities   [/api/v1/non-conformities]</t>
-  </si>
-  <si>
-    <t>/api/v1/non-conformities</t>
-  </si>
-  <si>
-    <t>Report a non-conformity finding</t>
-  </si>
-  <si>
-    <t>SURVEYOR,TO</t>
-  </si>
-  <si>
-    <t>/api/v1/non-conformities/:id/close</t>
-  </si>
-  <si>
-    <t>Close / resolve NC after correction</t>
-  </si>
-  <si>
-    <t>TO,TM</t>
-  </si>
-  <si>
-    <t>/api/v1/non-conformities/job/:jobId</t>
-  </si>
-  <si>
-    <t>Get all NCs for a job</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  🚨 Incidents   [/api/v1/incidents]</t>
-  </si>
-  <si>
-    <t>/api/v1/incidents</t>
-  </si>
-  <si>
-    <t>Report a new incident</t>
-  </si>
-  <si>
-    <t>CLIENT,ADMIN,GM,TM</t>
-  </si>
-  <si>
-    <t>List all incidents</t>
   </si>
   <si>
     <t>/api/v1/incidents/:id</t>
@@ -2259,7 +2244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H258"/>
+  <dimension ref="A1:H256"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -3759,7 +3744,7 @@
         <v>135</v>
       </c>
       <c r="E62" s="14" t="s">
-        <v>136</v>
+        <v>59</v>
       </c>
       <c r="F62" s="10" t="s">
         <v>15</v>
@@ -3779,13 +3764,13 @@
         <v>33</v>
       </c>
       <c r="C63" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="D63" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="D63" s="8" t="s">
+      <c r="E63" s="9" t="s">
         <v>138</v>
-      </c>
-      <c r="E63" s="9" t="s">
-        <v>59</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>15</v>
@@ -3811,7 +3796,7 @@
         <v>140</v>
       </c>
       <c r="E64" s="14" t="s">
-        <v>141</v>
+        <v>59</v>
       </c>
       <c r="F64" s="10" t="s">
         <v>15</v>
@@ -3827,17 +3812,17 @@
       <c r="A65" s="5">
         <v>56</v>
       </c>
-      <c r="B65" s="17" t="s">
-        <v>33</v>
+      <c r="B65" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C65" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D65" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="D65" s="8" t="s">
-        <v>143</v>
-      </c>
       <c r="E65" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>15</v>
@@ -3853,14 +3838,14 @@
       <c r="A66" s="11">
         <v>57</v>
       </c>
-      <c r="B66" s="16" t="s">
-        <v>30</v>
+      <c r="B66" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C66" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D66" s="13" t="s">
         <v>144</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>145</v>
       </c>
       <c r="E66" s="14" t="s">
         <v>61</v>
@@ -3879,17 +3864,17 @@
       <c r="A67" s="5">
         <v>58</v>
       </c>
-      <c r="B67" s="6" t="s">
-        <v>11</v>
+      <c r="B67" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C67" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D67" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="D67" s="8" t="s">
-        <v>147</v>
-      </c>
       <c r="E67" s="9" t="s">
-        <v>61</v>
+        <v>19</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>15</v>
@@ -3909,13 +3894,13 @@
         <v>30</v>
       </c>
       <c r="C68" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="D68" s="13" t="s">
         <v>148</v>
       </c>
-      <c r="D68" s="13" t="s">
-        <v>149</v>
-      </c>
       <c r="E68" s="14" t="s">
-        <v>19</v>
+        <v>61</v>
       </c>
       <c r="F68" s="10" t="s">
         <v>15</v>
@@ -3931,1131 +3916,1131 @@
       <c r="A69" s="5">
         <v>60</v>
       </c>
-      <c r="B69" s="16" t="s">
-        <v>30</v>
+      <c r="B69" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C69" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D69" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="E69" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G69" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H69" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="E69" s="9" t="s">
+      <c r="B70" s="4"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+    </row>
+    <row r="71" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
         <v>61</v>
       </c>
-      <c r="F69" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G69" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H69" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="11">
-        <v>61</v>
-      </c>
-      <c r="B70" s="6" t="s">
+      <c r="B71" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C71" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="D70" s="13" t="s">
+      <c r="D71" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="E70" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F70" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G70" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H70" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="71" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B71" s="4"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="4"/>
-      <c r="H71" s="4"/>
+      <c r="E71" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G71" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H71" s="8" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="72" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="5">
+      <c r="A72" s="11">
         <v>62</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C72" s="7" t="s">
+      <c r="C72" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D72" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="D72" s="8" t="s">
+      <c r="E72" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>63</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D73" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="E72" s="9" t="s">
+      <c r="E73" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G73" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H73" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="11">
+        <v>64</v>
+      </c>
+      <c r="B74" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="D74" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="E74" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="F72" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G72" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H72" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="11">
-        <v>63</v>
-      </c>
-      <c r="B73" s="6" t="s">
+      <c r="F74" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G74" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H74" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
+        <v>65</v>
+      </c>
+      <c r="B75" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C75" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>160</v>
+      </c>
+      <c r="E75" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G75" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H75" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="11">
+        <v>66</v>
+      </c>
+      <c r="B76" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D76" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="E76" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G76" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H76" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>67</v>
+      </c>
+      <c r="B77" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C77" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D73" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="E73" s="14" t="s">
+      <c r="D77" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="E77" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G77" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H77" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B78" s="4"/>
+      <c r="C78" s="4"/>
+      <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="4"/>
+      <c r="H78" s="4"/>
+    </row>
+    <row r="79" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
+        <v>68</v>
+      </c>
+      <c r="B79" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="E79" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H79" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="11">
+        <v>69</v>
+      </c>
+      <c r="B80" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>167</v>
+      </c>
+      <c r="D80" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E80" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="F73" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G73" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H73" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="5">
-        <v>64</v>
-      </c>
-      <c r="B74" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F74" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G74" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H74" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="11">
-        <v>65</v>
-      </c>
-      <c r="B75" s="17" t="s">
+      <c r="F80" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G80" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H80" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B81" s="4"/>
+      <c r="C81" s="4"/>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="4"/>
+      <c r="H81" s="4"/>
+    </row>
+    <row r="82" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="5">
+        <v>70</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="E82" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G82" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H82" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="11">
+        <v>71</v>
+      </c>
+      <c r="B83" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>171</v>
+      </c>
+      <c r="D83" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="E83" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G83" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H83" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="5">
+        <v>72</v>
+      </c>
+      <c r="B84" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="E84" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G84" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H84" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="11">
+        <v>73</v>
+      </c>
+      <c r="B85" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D85" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="E85" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G85" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H85" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="5">
+        <v>74</v>
+      </c>
+      <c r="B86" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C75" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="D75" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="E75" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F75" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G75" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H75" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="5">
-        <v>66</v>
-      </c>
-      <c r="B76" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="D76" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="F76" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G76" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H76" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="77" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="11">
-        <v>67</v>
-      </c>
-      <c r="B77" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C77" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="D77" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="E77" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="F77" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G77" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H77" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="78" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="5">
-        <v>68</v>
-      </c>
-      <c r="B78" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D78" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="E78" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="F78" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G78" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H78" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="79" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="B79" s="4"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="4"/>
-      <c r="H79" s="4"/>
-    </row>
-    <row r="80" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="5">
-        <v>69</v>
-      </c>
-      <c r="B80" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D80" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F80" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G80" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H80" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="81" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="11">
-        <v>70</v>
-      </c>
-      <c r="B81" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C81" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="D81" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="E81" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F81" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G81" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H81" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="82" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="B82" s="4"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="4"/>
-      <c r="H82" s="4"/>
-    </row>
-    <row r="83" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="5">
-        <v>71</v>
-      </c>
-      <c r="B83" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C83" s="7" t="s">
+      <c r="C86" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="D83" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="E83" s="9" t="s">
+      <c r="D86" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="E86" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="F83" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G83" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H83" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="84" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="11">
-        <v>72</v>
-      </c>
-      <c r="B84" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C84" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="D84" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="E84" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F84" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G84" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H84" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="85" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="5">
-        <v>73</v>
-      </c>
-      <c r="B85" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D85" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="E85" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="F85" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G85" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H85" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="86" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="11">
-        <v>74</v>
-      </c>
-      <c r="B86" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C86" s="12" t="s">
-        <v>180</v>
-      </c>
-      <c r="D86" s="13" t="s">
-        <v>181</v>
-      </c>
-      <c r="E86" s="14" t="s">
-        <v>88</v>
-      </c>
       <c r="F86" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G86" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H86" s="13" t="s">
+      <c r="H86" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="5">
+      <c r="A87" s="11">
         <v>75</v>
       </c>
       <c r="B87" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C87" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="D87" s="8" t="s">
+      <c r="C87" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="D87" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="E87" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G87" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H87" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="88" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="5">
+        <v>76</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="E87" s="9" t="s">
+      <c r="D88" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="E88" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="F87" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G87" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H87" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="88" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="11">
-        <v>76</v>
-      </c>
-      <c r="B88" s="17" t="s">
+      <c r="F88" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G88" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H88" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="89" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="11">
+        <v>77</v>
+      </c>
+      <c r="B89" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="D89" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="E89" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G89" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H89" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B90" s="4"/>
+      <c r="C90" s="4"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="4"/>
+    </row>
+    <row r="91" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="5">
+        <v>78</v>
+      </c>
+      <c r="B91" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H91" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="92" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="11">
+        <v>79</v>
+      </c>
+      <c r="B92" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="D92" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="E92" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G92" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H92" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="93" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="5">
+        <v>80</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G93" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H93" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="94" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="11">
+        <v>81</v>
+      </c>
+      <c r="B94" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="E94" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G94" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H94" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="95" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="5">
+        <v>82</v>
+      </c>
+      <c r="B95" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C88" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="D88" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="E88" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="F88" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G88" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H88" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="5">
-        <v>77</v>
-      </c>
-      <c r="B89" s="6" t="s">
+      <c r="C95" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G95" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H95" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="11">
+        <v>83</v>
+      </c>
+      <c r="B96" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="D96" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="E96" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F96" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G96" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H96" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="5">
+        <v>84</v>
+      </c>
+      <c r="B97" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C89" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D89" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="E89" s="9" t="s">
+      <c r="C97" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="E97" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="F89" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G89" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H89" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="90" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="11">
-        <v>78</v>
-      </c>
-      <c r="B90" s="18" t="s">
+      <c r="F97" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G97" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H97" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="98" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="11">
+        <v>85</v>
+      </c>
+      <c r="B98" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="D98" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="E98" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G98" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H98" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="5">
+        <v>86</v>
+      </c>
+      <c r="B99" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="C90" s="12" t="s">
-        <v>177</v>
-      </c>
-      <c r="D90" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="E90" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F90" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G90" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H90" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="91" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B91" s="4"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="4"/>
-      <c r="H91" s="4"/>
-    </row>
-    <row r="92" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="5">
-        <v>79</v>
-      </c>
-      <c r="B92" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D92" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="E92" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F92" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H92" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="93" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="11">
-        <v>80</v>
-      </c>
-      <c r="B93" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C93" s="12" t="s">
-        <v>191</v>
-      </c>
-      <c r="D93" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E93" s="14" t="s">
+      <c r="C99" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G99" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H99" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="100" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="11">
+        <v>87</v>
+      </c>
+      <c r="B100" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="D100" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="E100" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F93" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G93" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H93" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="94" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="5">
-        <v>81</v>
-      </c>
-      <c r="B94" s="6" t="s">
+      <c r="F100" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G100" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H100" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="5">
+        <v>88</v>
+      </c>
+      <c r="B101" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G101" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H101" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="102" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="11">
+        <v>89</v>
+      </c>
+      <c r="B102" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C94" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="D94" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="E94" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F94" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G94" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H94" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="95" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="11">
-        <v>82</v>
-      </c>
-      <c r="B95" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C95" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="D95" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="E95" s="14" t="s">
+      <c r="C102" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="D102" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="E102" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G102" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H102" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="5">
+        <v>90</v>
+      </c>
+      <c r="B103" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="E103" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F95" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G95" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H95" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="96" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="5">
-        <v>83</v>
-      </c>
-      <c r="B96" s="17" t="s">
+      <c r="F103" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G103" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H103" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="104" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="11">
+        <v>91</v>
+      </c>
+      <c r="B104" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="D104" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="E104" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F104" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G104" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H104" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="105" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="5">
+        <v>92</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F105" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G105" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H105" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="106" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="11">
+        <v>93</v>
+      </c>
+      <c r="B106" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C96" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="D96" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="E96" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F96" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G96" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H96" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="97" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="11">
-        <v>84</v>
-      </c>
-      <c r="B97" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C97" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="D97" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="E97" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="F97" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G97" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H97" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="98" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="5">
-        <v>85</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D98" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="E98" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F98" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G98" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H98" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="99" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="11">
-        <v>86</v>
-      </c>
-      <c r="B99" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C99" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="D99" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="E99" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="F99" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G99" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H99" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="100" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="5">
-        <v>87</v>
-      </c>
-      <c r="B100" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D100" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="E100" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F100" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G100" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H100" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="101" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="11">
-        <v>88</v>
-      </c>
-      <c r="B101" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C101" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="D101" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="E101" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F101" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G101" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H101" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="102" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="5">
-        <v>89</v>
-      </c>
-      <c r="B102" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="D102" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="E102" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="F102" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G102" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H102" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="11">
-        <v>90</v>
-      </c>
-      <c r="B103" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C103" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="D103" s="13" t="s">
-        <v>209</v>
-      </c>
-      <c r="E103" s="14" t="s">
+      <c r="C106" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="D106" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="E106" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F103" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G103" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H103" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="104" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="5">
-        <v>91</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D104" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="E104" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F104" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G104" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H104" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="105" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="11">
-        <v>92</v>
-      </c>
-      <c r="B105" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C105" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>213</v>
-      </c>
-      <c r="E105" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F105" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G105" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H105" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="106" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="5">
-        <v>93</v>
-      </c>
-      <c r="B106" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="D106" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="E106" s="9" t="s">
-        <v>19</v>
-      </c>
       <c r="F106" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G106" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H106" s="8" t="s">
+      <c r="H106" s="13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="11">
+      <c r="A107" s="5">
         <v>94</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C107" s="12" t="s">
-        <v>203</v>
-      </c>
-      <c r="D107" s="13" t="s">
+      <c r="C107" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="E107" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G107" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H107" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="108" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="11">
+        <v>95</v>
+      </c>
+      <c r="B108" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="D108" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="E108" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F108" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G108" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H108" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="109" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="5">
+        <v>96</v>
+      </c>
+      <c r="B109" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C109" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="E107" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F107" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G107" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H107" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="108" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="5">
-        <v>95</v>
-      </c>
-      <c r="B108" s="17" t="s">
+      <c r="D109" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="E109" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F109" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G109" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H109" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="11">
+        <v>97</v>
+      </c>
+      <c r="B110" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="E110" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F110" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G110" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H110" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="5">
+        <v>98</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="E111" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F111" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G111" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H111" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="112" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="11">
+        <v>99</v>
+      </c>
+      <c r="B112" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="D112" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="E112" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F112" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G112" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H112" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="5">
+        <v>100</v>
+      </c>
+      <c r="B113" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C108" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D108" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="E108" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F108" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G108" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H108" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="109" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="11">
-        <v>96</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C109" s="12" t="s">
-        <v>219</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="E109" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F109" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G109" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H109" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="110" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="5">
-        <v>97</v>
-      </c>
-      <c r="B110" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C110" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="D110" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="E110" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F110" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G110" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H110" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="111" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="11">
-        <v>98</v>
-      </c>
-      <c r="B111" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C111" s="12" t="s">
-        <v>222</v>
-      </c>
-      <c r="D111" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="E111" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F111" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G111" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H111" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="112" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="5">
-        <v>99</v>
-      </c>
-      <c r="B112" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C112" s="7" t="s">
+      <c r="C113" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="D112" s="8" t="s">
+      <c r="D113" s="8" t="s">
         <v>225</v>
       </c>
-      <c r="E112" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F112" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G112" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H112" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="113" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="11">
-        <v>100</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C113" s="12" t="s">
+      <c r="E113" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F113" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G113" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H113" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="11">
+        <v>101</v>
+      </c>
+      <c r="B114" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C114" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="D113" s="13" t="s">
+      <c r="D114" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="E113" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F113" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G113" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H113" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="114" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="5">
-        <v>101</v>
-      </c>
-      <c r="B114" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C114" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="D114" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="E114" s="9" t="s">
-        <v>19</v>
+      <c r="E114" s="14" t="s">
+        <v>88</v>
       </c>
       <c r="F114" s="10" t="s">
         <v>15</v>
@@ -5063,24 +5048,24 @@
       <c r="G114" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H114" s="8" t="s">
+      <c r="H114" s="13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="11">
+      <c r="A115" s="5">
         <v>102</v>
       </c>
       <c r="B115" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C115" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="E115" s="14" t="s">
+      <c r="C115" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="E115" s="9" t="s">
         <v>88</v>
       </c>
       <c r="F115" s="10" t="s">
@@ -5089,151 +5074,151 @@
       <c r="G115" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H115" s="13" t="s">
+      <c r="H115" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="5">
+      <c r="A116" s="11">
         <v>103</v>
       </c>
       <c r="B116" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C116" s="7" t="s">
+      <c r="C116" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="D116" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="E116" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="F116" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G116" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H116" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="117" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="5">
+        <v>104</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C117" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="D116" s="8" t="s">
+      <c r="D117" s="8" t="s">
         <v>233</v>
       </c>
-      <c r="E116" s="9" t="s">
+      <c r="E117" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="F116" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G116" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H116" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="117" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="11">
-        <v>104</v>
-      </c>
-      <c r="B117" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C117" s="12" t="s">
+      <c r="F117" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G117" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H117" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="11">
+        <v>105</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C118" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="D117" s="13" t="s">
+      <c r="D118" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="E117" s="14" t="s">
+      <c r="E118" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F117" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G117" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H117" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="118" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="5">
-        <v>105</v>
-      </c>
-      <c r="B118" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C118" s="7" t="s">
+      <c r="F118" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G118" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H118" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="119" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="D118" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="E118" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F118" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G118" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H118" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="119" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="11">
-        <v>106</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C119" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="D119" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="E119" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="F119" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G119" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H119" s="13" t="s">
-        <v>16</v>
-      </c>
+      <c r="B119" s="4"/>
+      <c r="C119" s="4"/>
+      <c r="D119" s="4"/>
+      <c r="E119" s="4"/>
+      <c r="F119" s="4"/>
+      <c r="G119" s="4"/>
+      <c r="H119" s="4"/>
     </row>
     <row r="120" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
+        <v>106</v>
+      </c>
+      <c r="B120" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C120" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="E120" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="F120" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G120" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H120" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="121" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="11">
         <v>107</v>
       </c>
-      <c r="B120" s="6" t="s">
+      <c r="B121" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C120" s="7" t="s">
-        <v>240</v>
-      </c>
-      <c r="D120" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="E120" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F120" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G120" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H120" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="121" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B121" s="4"/>
-      <c r="C121" s="4"/>
-      <c r="D121" s="4"/>
-      <c r="E121" s="4"/>
-      <c r="F121" s="4"/>
-      <c r="G121" s="4"/>
-      <c r="H121" s="4"/>
+      <c r="C121" s="12" t="s">
+        <v>237</v>
+      </c>
+      <c r="D121" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="E121" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F121" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G121" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H121" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="122" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
@@ -5243,13 +5228,13 @@
         <v>30</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E122" s="9" t="s">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="F122" s="10" t="s">
         <v>15</v>
@@ -5265,17 +5250,17 @@
       <c r="A123" s="11">
         <v>109</v>
       </c>
-      <c r="B123" s="6" t="s">
-        <v>11</v>
+      <c r="B123" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C123" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D123" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="D123" s="13" t="s">
-        <v>245</v>
-      </c>
       <c r="E123" s="14" t="s">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="F123" s="10" t="s">
         <v>15</v>
@@ -5291,14 +5276,14 @@
       <c r="A124" s="5">
         <v>110</v>
       </c>
-      <c r="B124" s="16" t="s">
-        <v>30</v>
+      <c r="B124" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E124" s="9" t="s">
         <v>40</v>
@@ -5317,107 +5302,107 @@
       <c r="A125" s="11">
         <v>111</v>
       </c>
-      <c r="B125" s="16" t="s">
-        <v>30</v>
+      <c r="B125" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="C125" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D125" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="E125" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F125" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G125" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H125" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="126" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B126" s="4"/>
+      <c r="C126" s="4"/>
+      <c r="D126" s="4"/>
+      <c r="E126" s="4"/>
+      <c r="F126" s="4"/>
+      <c r="G126" s="4"/>
+      <c r="H126" s="4"/>
+    </row>
+    <row r="127" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="5">
+        <v>112</v>
+      </c>
+      <c r="B127" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="D127" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="D125" s="13" t="s">
+      <c r="E127" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="E125" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F125" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G125" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H125" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="126" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="5">
-        <v>112</v>
-      </c>
-      <c r="B126" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="D126" s="8" t="s">
+      <c r="F127" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G127" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H127" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="128" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" s="11">
+        <v>113</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C128" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="E126" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F126" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G126" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H126" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="127" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="11">
-        <v>113</v>
-      </c>
-      <c r="B127" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C127" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D127" s="13" t="s">
+      <c r="D128" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="E127" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F127" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G127" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H127" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="128" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="B128" s="4"/>
-      <c r="C128" s="4"/>
-      <c r="D128" s="4"/>
-      <c r="E128" s="4"/>
-      <c r="F128" s="4"/>
-      <c r="G128" s="4"/>
-      <c r="H128" s="4"/>
+      <c r="E128" s="14" t="s">
+        <v>249</v>
+      </c>
+      <c r="F128" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G128" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H128" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="129" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>114</v>
       </c>
-      <c r="B129" s="16" t="s">
-        <v>30</v>
+      <c r="B129" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C129" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D129" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D129" s="8" t="s">
-        <v>254</v>
-      </c>
       <c r="E129" s="9" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="F129" s="10" t="s">
         <v>15</v>
@@ -5433,17 +5418,17 @@
       <c r="A130" s="11">
         <v>115</v>
       </c>
-      <c r="B130" s="6" t="s">
-        <v>11</v>
+      <c r="B130" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D130" s="13" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E130" s="14" t="s">
-        <v>255</v>
+        <v>19</v>
       </c>
       <c r="F130" s="10" t="s">
         <v>15</v>
@@ -5459,17 +5444,17 @@
       <c r="A131" s="5">
         <v>116</v>
       </c>
-      <c r="B131" s="6" t="s">
-        <v>11</v>
+      <c r="B131" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>255</v>
+        <v>19</v>
       </c>
       <c r="F131" s="10" t="s">
         <v>15</v>
@@ -5485,17 +5470,17 @@
       <c r="A132" s="11">
         <v>117</v>
       </c>
-      <c r="B132" s="16" t="s">
-        <v>30</v>
+      <c r="B132" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="D132" s="13" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E132" s="14" t="s">
-        <v>19</v>
+        <v>249</v>
       </c>
       <c r="F132" s="10" t="s">
         <v>15</v>
@@ -5511,17 +5496,17 @@
       <c r="A133" s="5">
         <v>118</v>
       </c>
-      <c r="B133" s="16" t="s">
-        <v>30</v>
+      <c r="B133" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>19</v>
+        <v>249</v>
       </c>
       <c r="F133" s="10" t="s">
         <v>15</v>
@@ -5537,104 +5522,104 @@
       <c r="A134" s="11">
         <v>119</v>
       </c>
-      <c r="B134" s="6" t="s">
-        <v>11</v>
+      <c r="B134" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="C134" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="D134" s="13" t="s">
+        <v>261</v>
+      </c>
+      <c r="E134" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F134" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G134" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H134" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="135" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="D134" s="13" t="s">
+      <c r="B135" s="4"/>
+      <c r="C135" s="4"/>
+      <c r="D135" s="4"/>
+      <c r="E135" s="4"/>
+      <c r="F135" s="4"/>
+      <c r="G135" s="4"/>
+      <c r="H135" s="4"/>
+    </row>
+    <row r="136" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" s="5">
+        <v>120</v>
+      </c>
+      <c r="B136" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C136" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="D136" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="E134" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="F134" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G134" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H134" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="135" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="5">
-        <v>120</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C135" s="7" t="s">
+      <c r="E136" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F136" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G136" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H136" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="11">
+        <v>121</v>
+      </c>
+      <c r="B137" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C137" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="D135" s="8" t="s">
+      <c r="D137" s="13" t="s">
         <v>266</v>
       </c>
-      <c r="E135" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="F135" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G135" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H135" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="136" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="11">
-        <v>121</v>
-      </c>
-      <c r="B136" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C136" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="D136" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="E136" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F136" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G136" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H136" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="137" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A137" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="B137" s="4"/>
-      <c r="C137" s="4"/>
-      <c r="D137" s="4"/>
-      <c r="E137" s="4"/>
-      <c r="F137" s="4"/>
-      <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
+      <c r="E137" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F137" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G137" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H137" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="138" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
         <v>122</v>
       </c>
-      <c r="B138" s="16" t="s">
-        <v>30</v>
+      <c r="B138" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D138" s="8" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E138" s="9" t="s">
         <v>19</v>
@@ -5649,140 +5634,140 @@
         <v>16</v>
       </c>
     </row>
-    <row r="139" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="11">
-        <v>123</v>
-      </c>
-      <c r="B139" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C139" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="D139" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="E139" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="F139" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G139" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H139" s="13" t="s">
-        <v>16</v>
-      </c>
+    <row r="139" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B139" s="4"/>
+      <c r="C139" s="4"/>
+      <c r="D139" s="4"/>
+      <c r="E139" s="4"/>
+      <c r="F139" s="4"/>
+      <c r="G139" s="4"/>
+      <c r="H139" s="4"/>
     </row>
     <row r="140" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="5">
+        <v>123</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="E140" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F140" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G140" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H140" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" s="11">
         <v>124</v>
       </c>
-      <c r="B140" s="17" t="s">
+      <c r="B141" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C140" s="7" t="s">
+      <c r="C141" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="D141" s="13" t="s">
         <v>273</v>
       </c>
-      <c r="D140" s="8" t="s">
+      <c r="E141" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F141" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G141" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H141" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="142" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="E140" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F140" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G140" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H140" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="141" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A141" s="4" t="s">
+      <c r="B142" s="4"/>
+      <c r="C142" s="4"/>
+      <c r="D142" s="4"/>
+      <c r="E142" s="4"/>
+      <c r="F142" s="4"/>
+      <c r="G142" s="4"/>
+      <c r="H142" s="4"/>
+    </row>
+    <row r="143" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A143" s="5">
+        <v>125</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="B141" s="4"/>
-      <c r="C141" s="4"/>
-      <c r="D141" s="4"/>
-      <c r="E141" s="4"/>
-      <c r="F141" s="4"/>
-      <c r="G141" s="4"/>
-      <c r="H141" s="4"/>
-    </row>
-    <row r="142" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A142" s="5">
-        <v>125</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C142" s="7" t="s">
+      <c r="D143" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="D142" s="8" t="s">
+      <c r="E143" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="E142" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F142" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G142" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H142" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="143" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A143" s="11">
+      <c r="F143" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G143" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H143" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="144" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A144" s="11">
         <v>126</v>
       </c>
-      <c r="B143" s="17" t="s">
+      <c r="B144" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C143" s="12" t="s">
+      <c r="C144" s="12" t="s">
         <v>278</v>
       </c>
-      <c r="D143" s="13" t="s">
+      <c r="D144" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="E143" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F143" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G143" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H143" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="144" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A144" s="4" t="s">
+      <c r="E144" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="B144" s="4"/>
-      <c r="C144" s="4"/>
-      <c r="D144" s="4"/>
-      <c r="E144" s="4"/>
-      <c r="F144" s="4"/>
-      <c r="G144" s="4"/>
-      <c r="H144" s="4"/>
+      <c r="F144" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G144" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H144" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="145" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
         <v>127</v>
       </c>
-      <c r="B145" s="6" t="s">
-        <v>11</v>
+      <c r="B145" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C145" s="7" t="s">
         <v>281</v>
@@ -5791,97 +5776,97 @@
         <v>282</v>
       </c>
       <c r="E145" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="F145" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G145" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H145" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="146" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="F145" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G145" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H145" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="146" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A146" s="11">
-        <v>128</v>
-      </c>
-      <c r="B146" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C146" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="D146" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="E146" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="F146" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G146" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H146" s="13" t="s">
-        <v>16</v>
-      </c>
+      <c r="B146" s="4"/>
+      <c r="C146" s="4"/>
+      <c r="D146" s="4"/>
+      <c r="E146" s="4"/>
+      <c r="F146" s="4"/>
+      <c r="G146" s="4"/>
+      <c r="H146" s="4"/>
     </row>
     <row r="147" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
+        <v>128</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C147" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>285</v>
+      </c>
+      <c r="E147" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F147" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G147" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H147" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="148" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="11">
         <v>129</v>
       </c>
-      <c r="B147" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C147" s="7" t="s">
+      <c r="B148" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="D148" s="13" t="s">
         <v>287</v>
       </c>
-      <c r="D147" s="8" t="s">
+      <c r="E148" s="14" t="s">
         <v>288</v>
       </c>
-      <c r="E147" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="F147" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G147" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H147" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="148" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A148" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B148" s="4"/>
-      <c r="C148" s="4"/>
-      <c r="D148" s="4"/>
-      <c r="E148" s="4"/>
-      <c r="F148" s="4"/>
-      <c r="G148" s="4"/>
-      <c r="H148" s="4"/>
+      <c r="F148" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G148" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H148" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="149" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
         <v>130</v>
       </c>
-      <c r="B149" s="6" t="s">
-        <v>11</v>
+      <c r="B149" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C149" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D149" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="D149" s="8" t="s">
-        <v>291</v>
-      </c>
       <c r="E149" s="9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F149" s="10" t="s">
         <v>15</v>
@@ -5897,91 +5882,91 @@
       <c r="A150" s="11">
         <v>131</v>
       </c>
-      <c r="B150" s="16" t="s">
-        <v>30</v>
+      <c r="B150" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D150" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="E150" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F150" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G150" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H150" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="151" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="E150" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="F150" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G150" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H150" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="151" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A151" s="5">
+      <c r="B151" s="4"/>
+      <c r="C151" s="4"/>
+      <c r="D151" s="4"/>
+      <c r="E151" s="4"/>
+      <c r="F151" s="4"/>
+      <c r="G151" s="4"/>
+      <c r="H151" s="4"/>
+    </row>
+    <row r="152" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A152" s="5">
         <v>132</v>
       </c>
-      <c r="B151" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C151" s="7" t="s">
+      <c r="B152" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C152" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="D151" s="8" t="s">
+      <c r="D152" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="E151" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="F151" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G151" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H151" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="152" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A152" s="11">
+      <c r="E152" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F152" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G152" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H152" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A153" s="11">
         <v>133</v>
       </c>
-      <c r="B152" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C152" s="12" t="s">
+      <c r="B153" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C153" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="D152" s="13" t="s">
+      <c r="D153" s="13" t="s">
         <v>297</v>
       </c>
-      <c r="E152" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F152" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G152" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H152" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="153" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A153" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B153" s="4"/>
-      <c r="C153" s="4"/>
-      <c r="D153" s="4"/>
-      <c r="E153" s="4"/>
-      <c r="F153" s="4"/>
-      <c r="G153" s="4"/>
-      <c r="H153" s="4"/>
+      <c r="E153" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="F153" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G153" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H153" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="154" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
@@ -5991,13 +5976,13 @@
         <v>30</v>
       </c>
       <c r="C154" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="D154" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="D154" s="8" t="s">
-        <v>300</v>
-      </c>
       <c r="E154" s="9" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="F154" s="10" t="s">
         <v>15</v>
@@ -6013,17 +5998,17 @@
       <c r="A155" s="11">
         <v>135</v>
       </c>
-      <c r="B155" s="16" t="s">
-        <v>30</v>
+      <c r="B155" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C155" s="12" t="s">
+        <v>300</v>
+      </c>
+      <c r="D155" s="13" t="s">
         <v>301</v>
       </c>
-      <c r="D155" s="13" t="s">
-        <v>302</v>
-      </c>
       <c r="E155" s="14" t="s">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="F155" s="10" t="s">
         <v>15</v>
@@ -6039,17 +6024,17 @@
       <c r="A156" s="5">
         <v>136</v>
       </c>
-      <c r="B156" s="16" t="s">
-        <v>30</v>
+      <c r="B156" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C156" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D156" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="D156" s="8" t="s">
-        <v>304</v>
-      </c>
       <c r="E156" s="9" t="s">
-        <v>292</v>
+        <v>59</v>
       </c>
       <c r="F156" s="10" t="s">
         <v>15</v>
@@ -6069,13 +6054,13 @@
         <v>11</v>
       </c>
       <c r="C157" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="D157" s="13" t="s">
         <v>305</v>
       </c>
-      <c r="D157" s="13" t="s">
-        <v>306</v>
-      </c>
       <c r="E157" s="14" t="s">
-        <v>59</v>
+        <v>120</v>
       </c>
       <c r="F157" s="10" t="s">
         <v>15</v>
@@ -6091,14 +6076,14 @@
       <c r="A158" s="5">
         <v>138</v>
       </c>
-      <c r="B158" s="17" t="s">
-        <v>33</v>
+      <c r="B158" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C158" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="D158" s="8" t="s">
         <v>307</v>
-      </c>
-      <c r="D158" s="8" t="s">
-        <v>308</v>
       </c>
       <c r="E158" s="9" t="s">
         <v>59</v>
@@ -6117,14 +6102,14 @@
       <c r="A159" s="11">
         <v>139</v>
       </c>
-      <c r="B159" s="6" t="s">
-        <v>11</v>
+      <c r="B159" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C159" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="D159" s="13" t="s">
         <v>309</v>
-      </c>
-      <c r="D159" s="13" t="s">
-        <v>310</v>
       </c>
       <c r="E159" s="14" t="s">
         <v>120</v>
@@ -6147,87 +6132,87 @@
         <v>11</v>
       </c>
       <c r="C160" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="D160" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="D160" s="8" t="s">
+      <c r="E160" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F160" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G160" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H160" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="161" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
         <v>312</v>
       </c>
-      <c r="E160" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F160" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G160" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H160" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="161" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A161" s="11">
-        <v>141</v>
-      </c>
-      <c r="B161" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C161" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="D161" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="E161" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F161" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G161" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H161" s="13" t="s">
-        <v>16</v>
-      </c>
+      <c r="B161" s="4"/>
+      <c r="C161" s="4"/>
+      <c r="D161" s="4"/>
+      <c r="E161" s="4"/>
+      <c r="F161" s="4"/>
+      <c r="G161" s="4"/>
+      <c r="H161" s="4"/>
     </row>
     <row r="162" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" s="5">
+        <v>141</v>
+      </c>
+      <c r="B162" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C162" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="D162" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="E162" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F162" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G162" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H162" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="163" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="11">
         <v>142</v>
       </c>
-      <c r="B162" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C162" s="7" t="s">
+      <c r="B163" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C163" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="D162" s="8" t="s">
+      <c r="D163" s="13" t="s">
         <v>316</v>
       </c>
-      <c r="E162" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F162" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G162" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H162" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="163" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A163" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B163" s="4"/>
-      <c r="C163" s="4"/>
-      <c r="D163" s="4"/>
-      <c r="E163" s="4"/>
-      <c r="F163" s="4"/>
-      <c r="G163" s="4"/>
-      <c r="H163" s="4"/>
+      <c r="E163" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F163" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G163" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H163" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="164" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="5">
@@ -6237,10 +6222,10 @@
         <v>30</v>
       </c>
       <c r="C164" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D164" s="8" t="s">
         <v>318</v>
-      </c>
-      <c r="D164" s="8" t="s">
-        <v>319</v>
       </c>
       <c r="E164" s="9" t="s">
         <v>59</v>
@@ -6263,103 +6248,103 @@
         <v>30</v>
       </c>
       <c r="C165" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="D165" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="D165" s="13" t="s">
+      <c r="E165" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F165" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G165" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H165" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="166" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="E165" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F165" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G165" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H165" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="166" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A166" s="5">
+      <c r="B166" s="4"/>
+      <c r="C166" s="4"/>
+      <c r="D166" s="4"/>
+      <c r="E166" s="4"/>
+      <c r="F166" s="4"/>
+      <c r="G166" s="4"/>
+      <c r="H166" s="4"/>
+    </row>
+    <row r="167" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A167" s="5">
         <v>145</v>
       </c>
-      <c r="B166" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C166" s="7" t="s">
+      <c r="B167" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C167" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="D166" s="8" t="s">
+      <c r="D167" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="E166" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F166" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G166" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H166" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="167" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A167" s="11">
+      <c r="E167" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F167" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G167" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H167" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="168" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A168" s="11">
         <v>146</v>
       </c>
-      <c r="B167" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C167" s="12" t="s">
+      <c r="B168" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C168" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="D168" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="D167" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="E167" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F167" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G167" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H167" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="168" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B168" s="4"/>
-      <c r="C168" s="4"/>
-      <c r="D168" s="4"/>
-      <c r="E168" s="4"/>
-      <c r="F168" s="4"/>
-      <c r="G168" s="4"/>
-      <c r="H168" s="4"/>
+      <c r="E168" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="F168" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G168" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H168" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="169" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="5">
         <v>147</v>
       </c>
-      <c r="B169" s="6" t="s">
-        <v>11</v>
+      <c r="B169" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="D169" s="8" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F169" s="10" t="s">
         <v>15</v>
@@ -6375,107 +6360,107 @@
       <c r="A170" s="11">
         <v>148</v>
       </c>
-      <c r="B170" s="16" t="s">
-        <v>30</v>
+      <c r="B170" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C170" s="12" t="s">
         <v>327</v>
       </c>
       <c r="D170" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="E170" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F170" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G170" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H170" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="171" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="E170" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="F170" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G170" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H170" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="171" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A171" s="5">
+      <c r="B171" s="4"/>
+      <c r="C171" s="4"/>
+      <c r="D171" s="4"/>
+      <c r="E171" s="4"/>
+      <c r="F171" s="4"/>
+      <c r="G171" s="4"/>
+      <c r="H171" s="4"/>
+    </row>
+    <row r="172" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" s="5">
         <v>149</v>
       </c>
-      <c r="B171" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C171" s="7" t="s">
+      <c r="B172" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C172" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="D171" s="8" t="s">
+      <c r="D172" s="8" t="s">
         <v>331</v>
       </c>
-      <c r="E171" s="9" t="s">
-        <v>207</v>
-      </c>
-      <c r="F171" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G171" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H171" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="172" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A172" s="11">
+      <c r="E172" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F172" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G172" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H172" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="173" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A173" s="11">
         <v>150</v>
       </c>
-      <c r="B172" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C172" s="12" t="s">
+      <c r="B173" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C173" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="D173" s="13" t="s">
         <v>332</v>
       </c>
-      <c r="D172" s="13" t="s">
-        <v>333</v>
-      </c>
-      <c r="E172" s="14" t="s">
+      <c r="E173" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F172" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G172" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H172" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="173" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A173" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B173" s="4"/>
-      <c r="C173" s="4"/>
-      <c r="D173" s="4"/>
-      <c r="E173" s="4"/>
-      <c r="F173" s="4"/>
-      <c r="G173" s="4"/>
-      <c r="H173" s="4"/>
+      <c r="F173" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G173" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H173" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="174" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="5">
         <v>151</v>
       </c>
-      <c r="B174" s="6" t="s">
-        <v>11</v>
+      <c r="B174" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="D174" s="8" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E174" s="9" t="s">
-        <v>292</v>
+        <v>120</v>
       </c>
       <c r="F174" s="10" t="s">
         <v>15</v>
@@ -6491,197 +6476,197 @@
       <c r="A175" s="11">
         <v>152</v>
       </c>
-      <c r="B175" s="16" t="s">
-        <v>30</v>
+      <c r="B175" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C175" s="12" t="s">
         <v>335</v>
       </c>
       <c r="D175" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="E175" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F175" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G175" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H175" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="176" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="E175" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F175" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G175" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H175" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="176" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A176" s="5">
+      <c r="B176" s="4"/>
+      <c r="C176" s="4"/>
+      <c r="D176" s="4"/>
+      <c r="E176" s="4"/>
+      <c r="F176" s="4"/>
+      <c r="G176" s="4"/>
+      <c r="H176" s="4"/>
+    </row>
+    <row r="177" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A177" s="5">
         <v>153</v>
       </c>
-      <c r="B176" s="17" t="s">
+      <c r="B177" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C177" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D177" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="E177" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="F177" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G177" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H177" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="178" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" s="11">
+        <v>154</v>
+      </c>
+      <c r="B178" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C176" s="7" t="s">
-        <v>338</v>
-      </c>
-      <c r="D176" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="E176" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="F176" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G176" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H176" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="177" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="11">
-        <v>154</v>
-      </c>
-      <c r="B177" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C177" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="D177" s="13" t="s">
+      <c r="C178" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="E177" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F177" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G177" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H177" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="178" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A178" s="4" t="s">
+      <c r="D178" s="13" t="s">
         <v>342</v>
       </c>
-      <c r="B178" s="4"/>
-      <c r="C178" s="4"/>
-      <c r="D178" s="4"/>
-      <c r="E178" s="4"/>
-      <c r="F178" s="4"/>
-      <c r="G178" s="4"/>
-      <c r="H178" s="4"/>
+      <c r="E178" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="F178" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G178" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H178" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="179" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="5">
         <v>155</v>
       </c>
-      <c r="B179" s="6" t="s">
-        <v>11</v>
+      <c r="B179" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C179" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D179" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="D179" s="8" t="s">
+      <c r="E179" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F179" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G179" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H179" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="180" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="E179" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="F179" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G179" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H179" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="180" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" s="11">
-        <v>156</v>
-      </c>
-      <c r="B180" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C180" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="D180" s="13" t="s">
-        <v>347</v>
-      </c>
-      <c r="E180" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="F180" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G180" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H180" s="13" t="s">
-        <v>16</v>
-      </c>
+      <c r="B180" s="4"/>
+      <c r="C180" s="4"/>
+      <c r="D180" s="4"/>
+      <c r="E180" s="4"/>
+      <c r="F180" s="4"/>
+      <c r="G180" s="4"/>
+      <c r="H180" s="4"/>
     </row>
     <row r="181" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="5">
+        <v>156</v>
+      </c>
+      <c r="B181" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C181" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="D181" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="E181" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F181" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G181" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H181" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="182" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A182" s="11">
         <v>157</v>
       </c>
-      <c r="B181" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C181" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="D181" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="E181" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="F181" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G181" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H181" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="182" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A182" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="B182" s="4"/>
-      <c r="C182" s="4"/>
-      <c r="D182" s="4"/>
-      <c r="E182" s="4"/>
-      <c r="F182" s="4"/>
-      <c r="G182" s="4"/>
-      <c r="H182" s="4"/>
+      <c r="B182" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C182" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D182" s="13" t="s">
+        <v>347</v>
+      </c>
+      <c r="E182" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="F182" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G182" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H182" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="183" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="5">
         <v>158</v>
       </c>
-      <c r="B183" s="6" t="s">
-        <v>11</v>
+      <c r="B183" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D183" s="8" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="F183" s="10" t="s">
         <v>15</v>
@@ -6697,181 +6682,181 @@
       <c r="A184" s="11">
         <v>159</v>
       </c>
-      <c r="B184" s="16" t="s">
-        <v>30</v>
+      <c r="B184" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C184" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="D184" s="13" t="s">
         <v>350</v>
       </c>
-      <c r="D184" s="13" t="s">
+      <c r="E184" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F184" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G184" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H184" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="185" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B185" s="4"/>
+      <c r="C185" s="4"/>
+      <c r="D185" s="4"/>
+      <c r="E185" s="4"/>
+      <c r="F185" s="4"/>
+      <c r="G185" s="4"/>
+      <c r="H185" s="4"/>
+    </row>
+    <row r="186" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A186" s="5">
+        <v>160</v>
+      </c>
+      <c r="B186" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C186" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="E184" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="F184" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G184" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H184" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="185" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A185" s="5">
-        <v>160</v>
-      </c>
-      <c r="B185" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C185" s="7" t="s">
+      <c r="D186" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="D185" s="8" t="s">
+      <c r="E186" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F186" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G186" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H186" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="187" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" s="11">
+        <v>161</v>
+      </c>
+      <c r="B187" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C187" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="D187" s="13" t="s">
         <v>354</v>
       </c>
-      <c r="E185" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F185" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G185" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H185" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="186" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" s="11">
-        <v>161</v>
-      </c>
-      <c r="B186" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C186" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="D186" s="13" t="s">
-        <v>355</v>
-      </c>
-      <c r="E186" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F186" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G186" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H186" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="187" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="B187" s="4"/>
-      <c r="C187" s="4"/>
-      <c r="D187" s="4"/>
-      <c r="E187" s="4"/>
-      <c r="F187" s="4"/>
-      <c r="G187" s="4"/>
-      <c r="H187" s="4"/>
+      <c r="E187" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F187" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G187" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H187" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="188" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="5">
         <v>162</v>
       </c>
-      <c r="B188" s="6" t="s">
-        <v>11</v>
+      <c r="B188" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C188" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="D188" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="E188" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="D188" s="8" t="s">
+      <c r="F188" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G188" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H188" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="189" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="E188" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="F188" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G188" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H188" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="189" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="11">
-        <v>163</v>
-      </c>
-      <c r="B189" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C189" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="D189" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="E189" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F189" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G189" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H189" s="13" t="s">
-        <v>16</v>
-      </c>
+      <c r="B189" s="4"/>
+      <c r="C189" s="4"/>
+      <c r="D189" s="4"/>
+      <c r="E189" s="4"/>
+      <c r="F189" s="4"/>
+      <c r="G189" s="4"/>
+      <c r="H189" s="4"/>
     </row>
     <row r="190" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" s="5">
+        <v>163</v>
+      </c>
+      <c r="B190" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C190" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="D190" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="E190" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F190" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G190" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H190" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="191" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" s="11">
         <v>164</v>
       </c>
-      <c r="B190" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C190" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="D190" s="8" t="s">
+      <c r="B191" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C191" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="E190" s="9" t="s">
+      <c r="D191" s="13" t="s">
         <v>362</v>
       </c>
-      <c r="F190" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G190" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H190" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="191" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A191" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="B191" s="4"/>
-      <c r="C191" s="4"/>
-      <c r="D191" s="4"/>
-      <c r="E191" s="4"/>
-      <c r="F191" s="4"/>
-      <c r="G191" s="4"/>
-      <c r="H191" s="4"/>
+      <c r="E191" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="F191" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G191" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H191" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="192" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" s="5">
@@ -6881,13 +6866,13 @@
         <v>30</v>
       </c>
       <c r="C192" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="D192" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="D192" s="8" t="s">
-        <v>365</v>
-      </c>
       <c r="E192" s="9" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F192" s="10" t="s">
         <v>15</v>
@@ -6903,17 +6888,17 @@
       <c r="A193" s="11">
         <v>166</v>
       </c>
-      <c r="B193" s="6" t="s">
-        <v>11</v>
+      <c r="B193" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="D193" s="13" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="E193" s="14" t="s">
-        <v>51</v>
+        <v>120</v>
       </c>
       <c r="F193" s="10" t="s">
         <v>15</v>
@@ -6929,107 +6914,107 @@
       <c r="A194" s="5">
         <v>167</v>
       </c>
-      <c r="B194" s="16" t="s">
-        <v>30</v>
+      <c r="B194" s="20" t="s">
+        <v>366</v>
       </c>
       <c r="C194" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="D194" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="D194" s="8" t="s">
+      <c r="E194" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F194" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G194" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H194" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="195" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="E194" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="F194" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G194" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H194" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="195" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A195" s="11">
-        <v>168</v>
-      </c>
-      <c r="B195" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C195" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="D195" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="E195" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F195" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G195" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H195" s="13" t="s">
-        <v>16</v>
-      </c>
+      <c r="B195" s="4"/>
+      <c r="C195" s="4"/>
+      <c r="D195" s="4"/>
+      <c r="E195" s="4"/>
+      <c r="F195" s="4"/>
+      <c r="G195" s="4"/>
+      <c r="H195" s="4"/>
     </row>
     <row r="196" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="5">
+        <v>168</v>
+      </c>
+      <c r="B196" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C196" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="D196" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="E196" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F196" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G196" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H196" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="197" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" s="11">
         <v>169</v>
       </c>
-      <c r="B196" s="20" t="s">
-        <v>371</v>
-      </c>
-      <c r="C196" s="7" t="s">
+      <c r="B197" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C197" s="12" t="s">
         <v>372</v>
       </c>
-      <c r="D196" s="8" t="s">
+      <c r="D197" s="13" t="s">
         <v>373</v>
       </c>
-      <c r="E196" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F196" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G196" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H196" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="197" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A197" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="B197" s="4"/>
-      <c r="C197" s="4"/>
-      <c r="D197" s="4"/>
-      <c r="E197" s="4"/>
-      <c r="F197" s="4"/>
-      <c r="G197" s="4"/>
-      <c r="H197" s="4"/>
+      <c r="E197" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F197" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G197" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H197" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="198" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" s="5">
         <v>170</v>
       </c>
-      <c r="B198" s="6" t="s">
-        <v>11</v>
+      <c r="B198" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D198" s="8" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E198" s="9" t="s">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="F198" s="10" t="s">
         <v>15</v>
@@ -7049,10 +7034,10 @@
         <v>30</v>
       </c>
       <c r="C199" s="12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D199" s="13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E199" s="14" t="s">
         <v>120</v>
@@ -7071,14 +7056,14 @@
       <c r="A200" s="5">
         <v>172</v>
       </c>
-      <c r="B200" s="16" t="s">
-        <v>30</v>
+      <c r="B200" s="20" t="s">
+        <v>366</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D200" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E200" s="9" t="s">
         <v>120</v>
@@ -7097,104 +7082,104 @@
       <c r="A201" s="11">
         <v>173</v>
       </c>
-      <c r="B201" s="16" t="s">
-        <v>30</v>
+      <c r="B201" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="C201" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="D201" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="E201" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F201" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G201" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H201" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="202" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="D201" s="13" t="s">
+      <c r="B202" s="4"/>
+      <c r="C202" s="4"/>
+      <c r="D202" s="4"/>
+      <c r="E202" s="4"/>
+      <c r="F202" s="4"/>
+      <c r="G202" s="4"/>
+      <c r="H202" s="4"/>
+    </row>
+    <row r="203" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" s="5">
+        <v>174</v>
+      </c>
+      <c r="B203" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C203" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="E201" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F201" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G201" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H201" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="202" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A202" s="5">
-        <v>174</v>
-      </c>
-      <c r="B202" s="20" t="s">
-        <v>371</v>
-      </c>
-      <c r="C202" s="7" t="s">
+      <c r="D203" s="8" t="s">
         <v>382</v>
       </c>
-      <c r="D202" s="8" t="s">
+      <c r="E203" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F203" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G203" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H203" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="204" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" s="11">
+        <v>175</v>
+      </c>
+      <c r="B204" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C204" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="D204" s="13" t="s">
         <v>383</v>
       </c>
-      <c r="E202" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="F202" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G202" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H202" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="203" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A203" s="11">
-        <v>175</v>
-      </c>
-      <c r="B203" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C203" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="D203" s="13" t="s">
-        <v>384</v>
-      </c>
-      <c r="E203" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F203" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G203" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H203" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="204" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A204" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="B204" s="4"/>
-      <c r="C204" s="4"/>
-      <c r="D204" s="4"/>
-      <c r="E204" s="4"/>
-      <c r="F204" s="4"/>
-      <c r="G204" s="4"/>
-      <c r="H204" s="4"/>
+      <c r="E204" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="F204" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G204" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H204" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="205" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="5">
         <v>176</v>
       </c>
-      <c r="B205" s="6" t="s">
-        <v>11</v>
+      <c r="B205" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="D205" s="8" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>19</v>
@@ -7213,147 +7198,133 @@
       <c r="A206" s="11">
         <v>177</v>
       </c>
-      <c r="B206" s="16" t="s">
-        <v>30</v>
+      <c r="B206" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C206" s="12" t="s">
         <v>386</v>
       </c>
       <c r="D206" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="E206" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="F206" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G206" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H206" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="207" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="E206" s="14" t="s">
+      <c r="B207" s="4"/>
+      <c r="C207" s="4"/>
+      <c r="D207" s="4"/>
+      <c r="E207" s="4"/>
+      <c r="F207" s="4"/>
+      <c r="G207" s="4"/>
+      <c r="H207" s="4"/>
+    </row>
+    <row r="208" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" s="5">
+        <v>178</v>
+      </c>
+      <c r="B208" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C208" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="D208" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="E208" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="F208" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G208" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H208" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="209" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" s="11">
+        <v>179</v>
+      </c>
+      <c r="B209" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C209" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="D209" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="E209" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="F209" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G209" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H209" s="13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="210" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B210" s="4"/>
+      <c r="C210" s="4"/>
+      <c r="D210" s="4"/>
+      <c r="E210" s="4"/>
+      <c r="F210" s="4"/>
+      <c r="G210" s="4"/>
+      <c r="H210" s="4"/>
+    </row>
+    <row r="211" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" s="5">
+        <v>180</v>
+      </c>
+      <c r="B211" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C211" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="D211" s="8" t="s">
+        <v>396</v>
+      </c>
+      <c r="E211" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="F206" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G206" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H206" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="207" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A207" s="5">
-        <v>178</v>
-      </c>
-      <c r="B207" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C207" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="D207" s="8" t="s">
-        <v>390</v>
-      </c>
-      <c r="E207" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F207" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G207" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H207" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="208" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A208" s="11">
-        <v>179</v>
-      </c>
-      <c r="B208" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C208" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="D208" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="E208" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="F208" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G208" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H208" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="209" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A209" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="B209" s="4"/>
-      <c r="C209" s="4"/>
-      <c r="D209" s="4"/>
-      <c r="E209" s="4"/>
-      <c r="F209" s="4"/>
-      <c r="G209" s="4"/>
-      <c r="H209" s="4"/>
-    </row>
-    <row r="210" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A210" s="5">
-        <v>180</v>
-      </c>
-      <c r="B210" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C210" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="D210" s="8" t="s">
-        <v>395</v>
-      </c>
-      <c r="E210" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="F210" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G210" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H210" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="211" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A211" s="11">
-        <v>181</v>
-      </c>
-      <c r="B211" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C211" s="12" t="s">
-        <v>397</v>
-      </c>
-      <c r="D211" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="E211" s="14" t="s">
-        <v>40</v>
-      </c>
       <c r="F211" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G211" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H211" s="13" t="s">
+      <c r="H211" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="212" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -7365,16 +7336,16 @@
     </row>
     <row r="213" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="5">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B213" s="16" t="s">
         <v>30</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D213" s="8" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E213" s="9" t="s">
         <v>19</v>
@@ -7382,8 +7353,8 @@
       <c r="F213" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G213" s="15" t="s">
-        <v>22</v>
+      <c r="G213" s="19" t="s">
+        <v>72</v>
       </c>
       <c r="H213" s="8" t="s">
         <v>16</v>
@@ -7391,7 +7362,7 @@
     </row>
     <row r="214" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -7403,57 +7374,71 @@
     </row>
     <row r="215" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="5">
+        <v>182</v>
+      </c>
+      <c r="B215" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C215" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="D215" s="8" t="s">
+        <v>402</v>
+      </c>
+      <c r="E215" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F215" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G215" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H215" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="216" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" s="11">
         <v>183</v>
       </c>
-      <c r="B215" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C215" s="7" t="s">
+      <c r="B216" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C216" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="D216" s="13" t="s">
         <v>403</v>
       </c>
-      <c r="D215" s="8" t="s">
-        <v>404</v>
-      </c>
-      <c r="E215" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="F215" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G215" s="19" t="s">
-        <v>72</v>
-      </c>
-      <c r="H215" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="216" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A216" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="B216" s="4"/>
-      <c r="C216" s="4"/>
-      <c r="D216" s="4"/>
-      <c r="E216" s="4"/>
-      <c r="F216" s="4"/>
-      <c r="G216" s="4"/>
-      <c r="H216" s="4"/>
+      <c r="E216" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F216" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G216" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H216" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="217" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="5">
         <v>184</v>
       </c>
-      <c r="B217" s="6" t="s">
-        <v>11</v>
+      <c r="B217" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D217" s="8" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E217" s="9" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>15</v>
@@ -7469,17 +7454,17 @@
       <c r="A218" s="11">
         <v>185</v>
       </c>
-      <c r="B218" s="16" t="s">
-        <v>30</v>
+      <c r="B218" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C218" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="D218" s="13" t="s">
         <v>406</v>
       </c>
-      <c r="D218" s="13" t="s">
-        <v>408</v>
-      </c>
       <c r="E218" s="14" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="F218" s="10" t="s">
         <v>15</v>
@@ -7495,17 +7480,17 @@
       <c r="A219" s="5">
         <v>186</v>
       </c>
-      <c r="B219" s="16" t="s">
-        <v>30</v>
+      <c r="B219" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D219" s="8" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E219" s="9" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>15</v>
@@ -7517,85 +7502,85 @@
         <v>16</v>
       </c>
     </row>
-    <row r="220" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A220" s="11">
-        <v>187</v>
-      </c>
-      <c r="B220" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C220" s="12" t="s">
-        <v>409</v>
-      </c>
-      <c r="D220" s="13" t="s">
-        <v>411</v>
-      </c>
-      <c r="E220" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F220" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G220" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H220" s="13" t="s">
-        <v>16</v>
-      </c>
+    <row r="220" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B220" s="4"/>
+      <c r="C220" s="4"/>
+      <c r="D220" s="4"/>
+      <c r="E220" s="4"/>
+      <c r="F220" s="4"/>
+      <c r="G220" s="4"/>
+      <c r="H220" s="4"/>
     </row>
     <row r="221" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="5">
-        <v>188</v>
-      </c>
-      <c r="B221" s="18" t="s">
-        <v>46</v>
+        <v>187</v>
+      </c>
+      <c r="B221" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C221" s="7" t="s">
         <v>409</v>
       </c>
       <c r="D221" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="E221" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F221" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G221" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H221" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="222" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" s="11">
+        <v>188</v>
+      </c>
+      <c r="B222" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C222" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="D222" s="13" t="s">
         <v>412</v>
       </c>
-      <c r="E221" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F221" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G221" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H221" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="222" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A222" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="B222" s="4"/>
-      <c r="C222" s="4"/>
-      <c r="D222" s="4"/>
-      <c r="E222" s="4"/>
-      <c r="F222" s="4"/>
-      <c r="G222" s="4"/>
-      <c r="H222" s="4"/>
+      <c r="E222" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F222" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G222" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H222" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="223" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" s="5">
         <v>189</v>
       </c>
-      <c r="B223" s="16" t="s">
-        <v>30</v>
+      <c r="B223" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C223" s="7" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="D223" s="8" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="E223" s="9" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>15</v>
@@ -7611,17 +7596,17 @@
       <c r="A224" s="11">
         <v>190</v>
       </c>
-      <c r="B224" s="16" t="s">
-        <v>30</v>
+      <c r="B224" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="D224" s="13" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E224" s="14" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F224" s="10" t="s">
         <v>15</v>
@@ -7637,14 +7622,14 @@
       <c r="A225" s="5">
         <v>191</v>
       </c>
-      <c r="B225" s="6" t="s">
-        <v>11</v>
+      <c r="B225" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D225" s="8" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E225" s="9" t="s">
         <v>40</v>
@@ -7663,14 +7648,14 @@
       <c r="A226" s="11">
         <v>192</v>
       </c>
-      <c r="B226" s="17" t="s">
-        <v>33</v>
+      <c r="B226" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C226" s="12" t="s">
         <v>416</v>
       </c>
       <c r="D226" s="13" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="E226" s="14" t="s">
         <v>40</v>
@@ -7689,14 +7674,14 @@
       <c r="A227" s="5">
         <v>193</v>
       </c>
-      <c r="B227" s="18" t="s">
-        <v>46</v>
+      <c r="B227" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C227" s="7" t="s">
         <v>416</v>
       </c>
       <c r="D227" s="8" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="E227" s="9" t="s">
         <v>40</v>
@@ -7715,14 +7700,14 @@
       <c r="A228" s="11">
         <v>194</v>
       </c>
-      <c r="B228" s="16" t="s">
-        <v>30</v>
+      <c r="B228" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="C228" s="12" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D228" s="13" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E228" s="14" t="s">
         <v>40</v>
@@ -7737,82 +7722,82 @@
         <v>16</v>
       </c>
     </row>
-    <row r="229" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A229" s="5">
+    <row r="229" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B229" s="4"/>
+      <c r="C229" s="4"/>
+      <c r="D229" s="4"/>
+      <c r="E229" s="4"/>
+      <c r="F229" s="4"/>
+      <c r="G229" s="4"/>
+      <c r="H229" s="4"/>
+    </row>
+    <row r="230" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230" s="5">
         <v>195</v>
       </c>
-      <c r="B229" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C229" s="7" t="s">
+      <c r="B230" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C230" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="D229" s="8" t="s">
+      <c r="D230" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="E230" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F230" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G230" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H230" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="231" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" s="11">
+        <v>196</v>
+      </c>
+      <c r="B231" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C231" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="E229" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F229" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G229" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H229" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="230" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A230" s="11">
-        <v>196</v>
-      </c>
-      <c r="B230" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C230" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="D230" s="13" t="s">
+      <c r="D231" s="13" t="s">
         <v>424</v>
       </c>
-      <c r="E230" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F230" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G230" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H230" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="231" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A231" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="B231" s="4"/>
-      <c r="C231" s="4"/>
-      <c r="D231" s="4"/>
-      <c r="E231" s="4"/>
-      <c r="F231" s="4"/>
-      <c r="G231" s="4"/>
-      <c r="H231" s="4"/>
+      <c r="E231" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F231" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G231" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H231" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="232" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="5">
         <v>197</v>
       </c>
-      <c r="B232" s="6" t="s">
-        <v>11</v>
+      <c r="B232" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C232" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="D232" s="8" t="s">
         <v>426</v>
-      </c>
-      <c r="D232" s="8" t="s">
-        <v>427</v>
       </c>
       <c r="E232" s="9" t="s">
         <v>14</v>
@@ -7831,17 +7816,17 @@
       <c r="A233" s="11">
         <v>198</v>
       </c>
-      <c r="B233" s="6" t="s">
-        <v>11</v>
+      <c r="B233" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C233" s="12" t="s">
+        <v>427</v>
+      </c>
+      <c r="D233" s="13" t="s">
         <v>428</v>
       </c>
-      <c r="D233" s="13" t="s">
-        <v>429</v>
-      </c>
       <c r="E233" s="14" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>15</v>
@@ -7857,107 +7842,107 @@
       <c r="A234" s="5">
         <v>199</v>
       </c>
-      <c r="B234" s="16" t="s">
-        <v>30</v>
+      <c r="B234" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C234" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D234" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="D234" s="8" t="s">
+      <c r="E234" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F234" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G234" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H234" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="235" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="E234" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F234" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G234" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H234" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="235" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A235" s="11">
-        <v>200</v>
-      </c>
-      <c r="B235" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C235" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="D235" s="13" t="s">
-        <v>433</v>
-      </c>
-      <c r="E235" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F235" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G235" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H235" s="13" t="s">
-        <v>16</v>
-      </c>
+      <c r="B235" s="4"/>
+      <c r="C235" s="4"/>
+      <c r="D235" s="4"/>
+      <c r="E235" s="4"/>
+      <c r="F235" s="4"/>
+      <c r="G235" s="4"/>
+      <c r="H235" s="4"/>
     </row>
     <row r="236" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="5">
+        <v>200</v>
+      </c>
+      <c r="B236" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C236" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="D236" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="E236" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F236" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G236" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H236" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="237" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" s="11">
         <v>201</v>
       </c>
-      <c r="B236" s="6" t="s">
+      <c r="B237" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C236" s="7" t="s">
+      <c r="C237" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D237" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="D236" s="8" t="s">
-        <v>435</v>
-      </c>
-      <c r="E236" s="9" t="s">
+      <c r="E237" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="F236" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G236" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H236" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="237" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A237" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="B237" s="4"/>
-      <c r="C237" s="4"/>
-      <c r="D237" s="4"/>
-      <c r="E237" s="4"/>
-      <c r="F237" s="4"/>
-      <c r="G237" s="4"/>
-      <c r="H237" s="4"/>
+      <c r="F237" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G237" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H237" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="238" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" s="5">
         <v>202</v>
       </c>
-      <c r="B238" s="16" t="s">
-        <v>30</v>
+      <c r="B238" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C238" s="7" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D238" s="8" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E238" s="9" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F238" s="10" t="s">
         <v>15</v>
@@ -7973,14 +7958,14 @@
       <c r="A239" s="11">
         <v>203</v>
       </c>
-      <c r="B239" s="6" t="s">
-        <v>11</v>
+      <c r="B239" s="18" t="s">
+        <v>46</v>
       </c>
       <c r="C239" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="D239" s="13" t="s">
         <v>437</v>
-      </c>
-      <c r="D239" s="13" t="s">
-        <v>439</v>
       </c>
       <c r="E239" s="14" t="s">
         <v>40</v>
@@ -7995,69 +7980,69 @@
         <v>16</v>
       </c>
     </row>
-    <row r="240" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A240" s="5">
+    <row r="240" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="B240" s="4"/>
+      <c r="C240" s="4"/>
+      <c r="D240" s="4"/>
+      <c r="E240" s="4"/>
+      <c r="F240" s="4"/>
+      <c r="G240" s="4"/>
+      <c r="H240" s="4"/>
+    </row>
+    <row r="241" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" s="5">
         <v>204</v>
       </c>
-      <c r="B240" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C240" s="7" t="s">
+      <c r="B241" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C241" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="D241" s="8" t="s">
         <v>440</v>
       </c>
-      <c r="D240" s="8" t="s">
+      <c r="E241" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="F241" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G241" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H241" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="242" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" s="11">
+        <v>205</v>
+      </c>
+      <c r="B242" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C242" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="E240" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F240" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G240" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H240" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="241" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A241" s="11">
-        <v>205</v>
-      </c>
-      <c r="B241" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="C241" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="D241" s="13" t="s">
+      <c r="D242" s="13" t="s">
         <v>442</v>
       </c>
-      <c r="E241" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F241" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G241" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H241" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="242" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A242" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="B242" s="4"/>
-      <c r="C242" s="4"/>
-      <c r="D242" s="4"/>
-      <c r="E242" s="4"/>
-      <c r="F242" s="4"/>
-      <c r="G242" s="4"/>
-      <c r="H242" s="4"/>
+      <c r="E242" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F242" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G242" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="H242" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="243" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="5">
@@ -8067,10 +8052,10 @@
         <v>30</v>
       </c>
       <c r="C243" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="D243" s="8" t="s">
         <v>444</v>
-      </c>
-      <c r="D243" s="8" t="s">
-        <v>445</v>
       </c>
       <c r="E243" s="9" t="s">
         <v>14</v>
@@ -8078,51 +8063,37 @@
       <c r="F243" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G243" s="10" t="s">
-        <v>15</v>
+      <c r="G243" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="H243" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="244" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A244" s="11">
-        <v>207</v>
-      </c>
-      <c r="B244" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C244" s="12" t="s">
-        <v>446</v>
-      </c>
-      <c r="D244" s="13" t="s">
-        <v>447</v>
-      </c>
-      <c r="E244" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F244" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G244" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="H244" s="13" t="s">
-        <v>16</v>
-      </c>
+    <row r="244" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B244" s="4"/>
+      <c r="C244" s="4"/>
+      <c r="D244" s="4"/>
+      <c r="E244" s="4"/>
+      <c r="F244" s="4"/>
+      <c r="G244" s="4"/>
+      <c r="H244" s="4"/>
     </row>
     <row r="245" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="5">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B245" s="16" t="s">
         <v>30</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D245" s="8" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E245" s="9" t="s">
         <v>14</v>
@@ -8130,24 +8101,38 @@
       <c r="F245" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G245" s="15" t="s">
-        <v>22</v>
+      <c r="G245" s="21" t="s">
+        <v>448</v>
       </c>
       <c r="H245" s="8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="246" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A246" s="4" t="s">
+    <row r="246" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246" s="11">
+        <v>208</v>
+      </c>
+      <c r="B246" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="C246" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="D246" s="13" t="s">
         <v>450</v>
       </c>
-      <c r="B246" s="4"/>
-      <c r="C246" s="4"/>
-      <c r="D246" s="4"/>
-      <c r="E246" s="4"/>
-      <c r="F246" s="4"/>
-      <c r="G246" s="4"/>
-      <c r="H246" s="4"/>
+      <c r="E246" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="F246" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G246" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="H246" s="13" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="247" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="5">
@@ -8169,7 +8154,7 @@
         <v>15</v>
       </c>
       <c r="G247" s="21" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="H247" s="8" t="s">
         <v>16</v>
@@ -8183,19 +8168,19 @@
         <v>30</v>
       </c>
       <c r="C248" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="D248" s="13" t="s">
         <v>454</v>
       </c>
-      <c r="D248" s="13" t="s">
-        <v>455</v>
-      </c>
       <c r="E248" s="14" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F248" s="10" t="s">
         <v>15</v>
       </c>
       <c r="G248" s="21" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="H248" s="13" t="s">
         <v>16</v>
@@ -8209,19 +8194,19 @@
         <v>30</v>
       </c>
       <c r="C249" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="D249" s="8" t="s">
         <v>456</v>
       </c>
-      <c r="D249" s="8" t="s">
-        <v>457</v>
-      </c>
       <c r="E249" s="9" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F249" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G249" s="21" t="s">
-        <v>453</v>
+      <c r="G249" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="H249" s="8" t="s">
         <v>16</v>
@@ -8231,14 +8216,14 @@
       <c r="A250" s="11">
         <v>212</v>
       </c>
-      <c r="B250" s="16" t="s">
-        <v>30</v>
+      <c r="B250" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C250" s="12" t="s">
+        <v>457</v>
+      </c>
+      <c r="D250" s="13" t="s">
         <v>458</v>
-      </c>
-      <c r="D250" s="13" t="s">
-        <v>459</v>
       </c>
       <c r="E250" s="14" t="s">
         <v>40</v>
@@ -8246,8 +8231,8 @@
       <c r="F250" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G250" s="21" t="s">
-        <v>453</v>
+      <c r="G250" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="H250" s="13" t="s">
         <v>16</v>
@@ -8261,10 +8246,10 @@
         <v>30</v>
       </c>
       <c r="C251" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="D251" s="8" t="s">
         <v>460</v>
-      </c>
-      <c r="D251" s="8" t="s">
-        <v>461</v>
       </c>
       <c r="E251" s="9" t="s">
         <v>40</v>
@@ -8272,8 +8257,8 @@
       <c r="F251" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G251" s="15" t="s">
-        <v>22</v>
+      <c r="G251" s="21" t="s">
+        <v>448</v>
       </c>
       <c r="H251" s="8" t="s">
         <v>16</v>
@@ -8283,14 +8268,14 @@
       <c r="A252" s="11">
         <v>214</v>
       </c>
-      <c r="B252" s="6" t="s">
-        <v>11</v>
+      <c r="B252" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C252" s="12" t="s">
+        <v>461</v>
+      </c>
+      <c r="D252" s="13" t="s">
         <v>462</v>
-      </c>
-      <c r="D252" s="13" t="s">
-        <v>463</v>
       </c>
       <c r="E252" s="14" t="s">
         <v>40</v>
@@ -8298,8 +8283,8 @@
       <c r="F252" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="G252" s="15" t="s">
-        <v>22</v>
+      <c r="G252" s="21" t="s">
+        <v>448</v>
       </c>
       <c r="H252" s="13" t="s">
         <v>16</v>
@@ -8309,14 +8294,14 @@
       <c r="A253" s="5">
         <v>215</v>
       </c>
-      <c r="B253" s="16" t="s">
-        <v>30</v>
+      <c r="B253" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C253" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="D253" s="8" t="s">
         <v>464</v>
-      </c>
-      <c r="D253" s="8" t="s">
-        <v>465</v>
       </c>
       <c r="E253" s="9" t="s">
         <v>40</v>
@@ -8325,7 +8310,7 @@
         <v>15</v>
       </c>
       <c r="G253" s="21" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="H253" s="8" t="s">
         <v>16</v>
@@ -8335,14 +8320,14 @@
       <c r="A254" s="11">
         <v>216</v>
       </c>
-      <c r="B254" s="16" t="s">
-        <v>30</v>
+      <c r="B254" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="C254" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="D254" s="13" t="s">
         <v>466</v>
-      </c>
-      <c r="D254" s="13" t="s">
-        <v>467</v>
       </c>
       <c r="E254" s="14" t="s">
         <v>40</v>
@@ -8351,7 +8336,7 @@
         <v>15</v>
       </c>
       <c r="G254" s="21" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="H254" s="13" t="s">
         <v>16</v>
@@ -8361,14 +8346,14 @@
       <c r="A255" s="5">
         <v>217</v>
       </c>
-      <c r="B255" s="6" t="s">
-        <v>11</v>
+      <c r="B255" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C255" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="D255" s="8" t="s">
         <v>468</v>
-      </c>
-      <c r="D255" s="8" t="s">
-        <v>469</v>
       </c>
       <c r="E255" s="9" t="s">
         <v>40</v>
@@ -8377,7 +8362,7 @@
         <v>15</v>
       </c>
       <c r="G255" s="21" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="H255" s="8" t="s">
         <v>16</v>
@@ -8387,14 +8372,14 @@
       <c r="A256" s="11">
         <v>218</v>
       </c>
-      <c r="B256" s="6" t="s">
-        <v>11</v>
+      <c r="B256" s="16" t="s">
+        <v>30</v>
       </c>
       <c r="C256" s="12" t="s">
+        <v>469</v>
+      </c>
+      <c r="D256" s="13" t="s">
         <v>470</v>
-      </c>
-      <c r="D256" s="13" t="s">
-        <v>471</v>
       </c>
       <c r="E256" s="14" t="s">
         <v>40</v>
@@ -8403,61 +8388,9 @@
         <v>15</v>
       </c>
       <c r="G256" s="21" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="H256" s="13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="257" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A257" s="5">
-        <v>219</v>
-      </c>
-      <c r="B257" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C257" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="D257" s="8" t="s">
-        <v>473</v>
-      </c>
-      <c r="E257" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="F257" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G257" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="H257" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="258" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A258" s="11">
-        <v>220</v>
-      </c>
-      <c r="B258" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C258" s="12" t="s">
-        <v>474</v>
-      </c>
-      <c r="D258" s="13" t="s">
-        <v>475</v>
-      </c>
-      <c r="E258" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="F258" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G258" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="H258" s="13" t="s">
         <v>16</v>
       </c>
     </row>
@@ -8472,35 +8405,35 @@
     <mergeCell ref="A31:H31"/>
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A71:H71"/>
-    <mergeCell ref="A79:H79"/>
-    <mergeCell ref="A82:H82"/>
-    <mergeCell ref="A91:H91"/>
-    <mergeCell ref="A121:H121"/>
-    <mergeCell ref="A128:H128"/>
-    <mergeCell ref="A137:H137"/>
-    <mergeCell ref="A141:H141"/>
-    <mergeCell ref="A144:H144"/>
-    <mergeCell ref="A148:H148"/>
-    <mergeCell ref="A153:H153"/>
-    <mergeCell ref="A163:H163"/>
-    <mergeCell ref="A168:H168"/>
-    <mergeCell ref="A173:H173"/>
-    <mergeCell ref="A178:H178"/>
-    <mergeCell ref="A182:H182"/>
-    <mergeCell ref="A187:H187"/>
-    <mergeCell ref="A191:H191"/>
-    <mergeCell ref="A197:H197"/>
-    <mergeCell ref="A204:H204"/>
-    <mergeCell ref="A209:H209"/>
+    <mergeCell ref="A70:H70"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A81:H81"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A119:H119"/>
+    <mergeCell ref="A126:H126"/>
+    <mergeCell ref="A135:H135"/>
+    <mergeCell ref="A139:H139"/>
+    <mergeCell ref="A142:H142"/>
+    <mergeCell ref="A146:H146"/>
+    <mergeCell ref="A151:H151"/>
+    <mergeCell ref="A161:H161"/>
+    <mergeCell ref="A166:H166"/>
+    <mergeCell ref="A171:H171"/>
+    <mergeCell ref="A176:H176"/>
+    <mergeCell ref="A180:H180"/>
+    <mergeCell ref="A185:H185"/>
+    <mergeCell ref="A189:H189"/>
+    <mergeCell ref="A195:H195"/>
+    <mergeCell ref="A202:H202"/>
+    <mergeCell ref="A207:H207"/>
+    <mergeCell ref="A210:H210"/>
     <mergeCell ref="A212:H212"/>
     <mergeCell ref="A214:H214"/>
-    <mergeCell ref="A216:H216"/>
-    <mergeCell ref="A222:H222"/>
-    <mergeCell ref="A231:H231"/>
-    <mergeCell ref="A237:H237"/>
-    <mergeCell ref="A242:H242"/>
-    <mergeCell ref="A246:H246"/>
+    <mergeCell ref="A220:H220"/>
+    <mergeCell ref="A229:H229"/>
+    <mergeCell ref="A235:H235"/>
+    <mergeCell ref="A240:H240"/>
+    <mergeCell ref="A244:H244"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -8519,7 +8452,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -8529,27 +8462,27 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
+        <v>472</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>473</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>475</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>476</v>
+      </c>
+      <c r="F2" s="23" t="s">
         <v>477</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>478</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>479</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>480</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>481</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="B3" s="25">
         <v>6</v>
@@ -8569,7 +8502,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="B4" s="30">
         <v>8</v>
@@ -8589,7 +8522,7 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="24" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="B5" s="25">
         <v>10</v>
@@ -8609,7 +8542,7 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B6" s="30">
         <v>5</v>
@@ -8629,7 +8562,7 @@
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B7" s="25">
         <v>12</v>
@@ -8649,13 +8582,13 @@
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B8" s="30">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="26">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D8" s="26">
         <v>0</v>
@@ -8664,12 +8597,12 @@
         <v>0</v>
       </c>
       <c r="F8" s="28">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="B9" s="25">
         <v>7</v>
@@ -8689,7 +8622,7 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="B10" s="30">
         <v>2</v>
@@ -8709,7 +8642,7 @@
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="B11" s="25">
         <v>8</v>
@@ -8729,13 +8662,13 @@
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="B12" s="30">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="26">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D12" s="26">
         <v>0</v>
@@ -8744,12 +8677,12 @@
         <v>1</v>
       </c>
       <c r="F12" s="28">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="24" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="B13" s="25">
         <v>6</v>
@@ -8769,7 +8702,7 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="B14" s="30">
         <v>8</v>
@@ -8789,7 +8722,7 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="B15" s="25">
         <v>3</v>
@@ -8809,7 +8742,7 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B16" s="30">
         <v>2</v>
@@ -8829,7 +8762,7 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="B17" s="25">
         <v>3</v>
@@ -8849,7 +8782,7 @@
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="B18" s="30">
         <v>4</v>
@@ -8869,7 +8802,7 @@
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="24" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B19" s="25">
         <v>9</v>
@@ -8889,7 +8822,7 @@
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="B20" s="30">
         <v>4</v>
@@ -8909,7 +8842,7 @@
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B21" s="25">
         <v>4</v>
@@ -8929,7 +8862,7 @@
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="B22" s="30">
         <v>4</v>
@@ -8949,7 +8882,7 @@
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="B23" s="25">
         <v>3</v>
@@ -8969,7 +8902,7 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B24" s="30">
         <v>4</v>
@@ -8989,7 +8922,7 @@
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B25" s="25">
         <v>3</v>
@@ -9009,7 +8942,7 @@
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B26" s="30">
         <v>5</v>
@@ -9029,7 +8962,7 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="24" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="B27" s="25">
         <v>6</v>
@@ -9049,7 +8982,7 @@
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B28" s="30">
         <v>4</v>
@@ -9069,7 +9002,7 @@
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="24" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="B29" s="25">
         <v>2</v>
@@ -9089,7 +9022,7 @@
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="B30" s="30">
         <v>1</v>
@@ -9109,7 +9042,7 @@
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="24" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="B31" s="25">
         <v>1</v>
@@ -9129,7 +9062,7 @@
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="B32" s="30">
         <v>5</v>
@@ -9149,7 +9082,7 @@
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="24" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="B33" s="25">
         <v>8</v>
@@ -9169,7 +9102,7 @@
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B34" s="30">
         <v>5</v>
@@ -9189,7 +9122,7 @@
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="24" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B35" s="25">
         <v>4</v>
@@ -9209,7 +9142,7 @@
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="B36" s="30">
         <v>3</v>
@@ -9229,7 +9162,7 @@
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="24" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="B37" s="25">
         <v>12</v>
@@ -9249,13 +9182,13 @@
     </row>
     <row r="38" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="31" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="B38" s="32">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C38" s="32">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D38" s="32">
         <v>0</v>
@@ -9264,12 +9197,12 @@
         <v>7</v>
       </c>
       <c r="F38" s="32">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="33" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="B40" s="33"/>
       <c r="C40" s="33"/>
@@ -9279,16 +9212,16 @@
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="34" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B41" s="35" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="D41" s="37" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>
